--- a/EPSS_Vehicle_System.xlsx
+++ b/EPSS_Vehicle_System.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22920" windowHeight="9465" activeTab="3"/>
+    <workbookView windowWidth="22920" windowHeight="9465" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Hubs" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="256">
   <si>
     <t>HubName</t>
   </si>
@@ -787,6 +787,18 @@
   </si>
   <si>
     <t>Zbirhan</t>
+  </si>
+  <si>
+    <t>demekerebih27@gmail.com</t>
+  </si>
+  <si>
+    <t>Dkerebih</t>
+  </si>
+  <si>
+    <t>gutetajenet1@gmail.com</t>
+  </si>
+  <si>
+    <t>Gguteta</t>
   </si>
 </sst>
 </file>
@@ -1477,7 +1489,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1518,9 +1530,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
@@ -2076,97 +2085,97 @@
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="13" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="12" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="13" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="12" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="13" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="13" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="12" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="13" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="12" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="13" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="12" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="13" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="12" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="13" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="12" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="13" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="14" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2196,7 +2205,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="4" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3354,7 +3363,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="29.5714285714286" customWidth="1"/>
@@ -3531,6 +3540,34 @@
         <v>237</v>
       </c>
     </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>252</v>
+      </c>
+      <c r="B13">
+        <v>1234</v>
+      </c>
+      <c r="C13" t="s">
+        <v>253</v>
+      </c>
+      <c r="D13" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>254</v>
+      </c>
+      <c r="B14">
+        <v>1234</v>
+      </c>
+      <c r="C14" t="s">
+        <v>255</v>
+      </c>
+      <c r="D14" t="s">
+        <v>237</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/EPSS_Vehicle_System.xlsx
+++ b/EPSS_Vehicle_System.xlsx
@@ -789,7 +789,7 @@
     <t>Zbirhan</t>
   </si>
   <si>
-    <t>demekerebih27@gmail.com</t>
+    <t>demekekerebih27@gmail.com</t>
   </si>
   <si>
     <t>Dkerebih</t>
@@ -826,6 +826,14 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
@@ -848,14 +856,6 @@
       <color theme="1"/>
       <name val="Arial"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1359,7 +1359,7 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1489,17 +1489,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
       <extLst>
         <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
@@ -1507,37 +1510,37 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -2085,97 +2088,97 @@
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="13" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="14" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="13" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="14" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="14" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="13" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="13" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="13" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="13" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="14" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="14" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="13" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="14" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="15" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2205,7 +2208,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2292,970 +2295,970 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" spans="1:3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:3">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:3">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:3">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:3">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:3">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:3">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:3">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="15" ht="15.75" spans="1:3">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:3">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="17" ht="15.75" spans="1:3">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="18" ht="15.75" spans="1:3">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="19" ht="15.75" spans="1:3">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="20" ht="15.75" spans="1:3">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="21" ht="15.75" spans="1:3">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="22" ht="15.75" spans="1:3">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="23" ht="15.75" spans="1:3">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="3" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="24" ht="15.75" spans="1:3">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="25" ht="15.75" spans="1:3">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="3" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="26" ht="15.75" spans="1:3">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="27" ht="15.75" spans="1:3">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="28" ht="15.75" spans="1:3">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="3" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="29" ht="15.75" spans="1:3">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="4" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="30" ht="15.75" spans="1:3">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="3" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="31" ht="15.75" spans="1:3">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="3" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="32" ht="15.75" spans="1:3">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="3" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="33" ht="15.75" spans="1:3">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="34" ht="15.75" spans="1:3">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="35" ht="15.75" spans="1:3">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="36" ht="15.75" spans="1:3">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="4" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="37" ht="15.75" spans="1:3">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="3" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="38" ht="15.75" spans="1:3">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="3" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="39" ht="15.75" spans="1:3">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="40" ht="15.75" spans="1:3">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="3" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="41" ht="15.75" spans="1:3">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="42" ht="15.75" spans="1:3">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="43" ht="15.75" spans="1:3">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="4" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="44" ht="15.75" spans="1:3">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="4" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="45" ht="15.75" spans="1:3">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="46" ht="15.75" spans="1:3">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="47" ht="15.75" spans="1:3">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="48" ht="15.75" spans="1:3">
-      <c r="A48" s="2" t="s">
+      <c r="A48" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="49" ht="15.75" spans="1:3">
-      <c r="A49" s="2" t="s">
+      <c r="A49" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="50" ht="15.75" spans="1:3">
-      <c r="A50" s="2" t="s">
+      <c r="A50" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="51" ht="15.75" spans="1:3">
-      <c r="A51" s="2" t="s">
+      <c r="A51" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="3" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="52" ht="15.75" spans="1:3">
-      <c r="A52" s="2" t="s">
+      <c r="A52" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="53" ht="15.75" spans="1:3">
-      <c r="A53" s="2" t="s">
+      <c r="A53" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="54" ht="15.75" spans="1:3">
-      <c r="A54" s="2" t="s">
+      <c r="A54" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="55" ht="15.75" spans="1:3">
-      <c r="A55" s="2" t="s">
+      <c r="A55" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="3" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="56" ht="15.75" spans="1:3">
-      <c r="A56" s="2" t="s">
+      <c r="A56" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="57" ht="15.75" spans="1:3">
-      <c r="A57" s="2" t="s">
+      <c r="A57" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C57" s="4" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="58" ht="15.75" spans="1:3">
-      <c r="A58" s="2" t="s">
+      <c r="A58" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="3" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="59" ht="15.75" spans="1:3">
-      <c r="A59" s="2" t="s">
+      <c r="A59" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="3" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="60" ht="15.75" spans="1:3">
-      <c r="A60" s="2" t="s">
+      <c r="A60" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="3" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="61" ht="15.75" spans="1:3">
-      <c r="A61" s="9" t="s">
+      <c r="A61" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="B61" s="9" t="s">
+      <c r="B61" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="C61" s="9" t="s">
+      <c r="C61" s="10" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="62" ht="15.75" spans="1:3">
-      <c r="A62" s="2" t="s">
+      <c r="A62" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="63" ht="15.75" spans="1:3">
-      <c r="A63" s="2" t="s">
+      <c r="A63" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="64" ht="15.75" spans="1:3">
-      <c r="A64" s="2" t="s">
+      <c r="A64" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="65" ht="15.75" spans="1:3">
-      <c r="A65" s="2" t="s">
+      <c r="A65" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B65" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="66" ht="15.75" spans="1:3">
-      <c r="A66" s="2" t="s">
+      <c r="A66" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B66" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C66" s="4" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="67" ht="15.75" spans="1:3">
-      <c r="A67" s="2" t="s">
+      <c r="A67" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="B67" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="68" ht="15.75" spans="1:3">
-      <c r="A68" s="2" t="s">
+      <c r="A68" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B68" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="69" ht="15.75" spans="1:3">
-      <c r="A69" s="2" t="s">
+      <c r="A69" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B69" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="3" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="70" ht="15.75" spans="1:3">
-      <c r="A70" s="2" t="s">
+      <c r="A70" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B70" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="3" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="71" ht="15.75" spans="1:3">
-      <c r="A71" s="2" t="s">
+      <c r="A71" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B71" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="72" ht="15.75" spans="1:3">
-      <c r="A72" s="9" t="s">
+      <c r="A72" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="B72" s="9" t="s">
+      <c r="B72" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C72" s="4" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="73" ht="15.75" spans="1:3">
-      <c r="A73" s="2" t="s">
+      <c r="A73" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B73" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="3" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="74" ht="15.75" spans="1:3">
-      <c r="A74" s="2" t="s">
+      <c r="A74" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B74" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="C74" s="4" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="75" ht="15.75" spans="1:3">
-      <c r="A75" s="2" t="s">
+      <c r="A75" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="B75" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="3" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="76" ht="15.75" spans="1:3">
-      <c r="A76" s="2" t="s">
+      <c r="A76" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B76" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C76" s="3" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="77" ht="15.75" spans="1:3">
-      <c r="A77" s="2" t="s">
+      <c r="A77" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B77" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C77" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="78" ht="15.75" spans="1:3">
-      <c r="A78" s="2" t="s">
+      <c r="A78" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="B78" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="79" ht="15.75" spans="1:3">
-      <c r="A79" s="2" t="s">
+      <c r="A79" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="B79" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C79" s="4" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="80" ht="15.75" spans="1:3">
-      <c r="A80" s="2" t="s">
+      <c r="A80" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B80" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C80" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="81" ht="15.75" spans="1:3">
-      <c r="A81" s="2" t="s">
+      <c r="A81" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="B81" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C81" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="82" ht="15.75" spans="1:3">
-      <c r="A82" s="2" t="s">
+      <c r="A82" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="B82" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C82" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="83" ht="15.75" spans="1:3">
-      <c r="A83" s="2" t="s">
+      <c r="A83" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="B83" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="C83" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="84" ht="15.75" spans="1:3">
-      <c r="A84" s="10" t="s">
+      <c r="A84" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="B84" s="10" t="s">
+      <c r="B84" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="C84" s="10" t="s">
+      <c r="C84" s="11" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="85" ht="15.75" spans="1:3">
-      <c r="A85" s="10" t="s">
+      <c r="A85" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="B85" s="10" t="s">
+      <c r="B85" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="C85" s="10" t="s">
+      <c r="C85" s="11" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="86" ht="15.75" spans="1:3">
-      <c r="A86" s="10" t="s">
+      <c r="A86" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="B86" s="10" t="s">
+      <c r="B86" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="C86" s="10" t="s">
+      <c r="C86" s="11" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="87" ht="15.75" spans="1:3">
-      <c r="A87" s="11" t="s">
+      <c r="A87" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="B87" s="11" t="s">
+      <c r="B87" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="C87" s="11" t="s">
+      <c r="C87" s="12" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="88" ht="15.75" spans="1:3">
-      <c r="A88" s="8" t="s">
+      <c r="A88" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="B88" s="8" t="s">
+      <c r="B88" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="C88" s="11" t="s">
+      <c r="C88" s="12" t="s">
         <v>41</v>
       </c>
     </row>
@@ -3280,77 +3283,77 @@
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:1">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:1">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:1">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:1">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:1">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:1">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:1">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:1">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="5" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="6" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="5" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="5" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="5" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="5" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="5" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3541,7 +3544,7 @@
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" t="s">
+      <c r="A13" s="2" t="s">
         <v>252</v>
       </c>
       <c r="B13">
@@ -3569,6 +3572,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A13" r:id="rId1" display="demekekerebih27@gmail.com"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/EPSS_Vehicle_System.xlsx
+++ b/EPSS_Vehicle_System.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22920" windowHeight="9465" activeTab="4"/>
+    <workbookView windowWidth="23160" windowHeight="8880" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Hubs" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="257">
   <si>
     <t>HubName</t>
   </si>
@@ -735,22 +735,25 @@
     <t>Gabdeta</t>
   </si>
   <si>
+    <t>Assignment Approver</t>
+  </si>
+  <si>
+    <t>teferikibru7@gmail.com</t>
+  </si>
+  <si>
+    <t>Kteferi</t>
+  </si>
+  <si>
     <t>Assigner</t>
   </si>
   <si>
-    <t>teferikibru7@gmail.com</t>
-  </si>
-  <si>
-    <t>Kteferi</t>
+    <t>kalkidana671@gmail.com</t>
+  </si>
+  <si>
+    <t>Kakililu</t>
   </si>
   <si>
     <t>Requester</t>
-  </si>
-  <si>
-    <t>kalkidana671@gmail.com</t>
-  </si>
-  <si>
-    <t>Kakililu</t>
   </si>
   <si>
     <t>atnasiyasheleme0@gmail.com</t>
@@ -828,7 +831,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -860,7 +863,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1359,12 +1362,12 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -1489,14 +1492,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2088,97 +2094,97 @@
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="15" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="14" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="15" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="15" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="14" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="14" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="15" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="15" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="14" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="15" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="15" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="14" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="15" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="16" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2208,7 +2214,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2295,970 +2301,970 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" spans="1:3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:3">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:3">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:3">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:3">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:3">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="15" ht="15.75" spans="1:3">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:3">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="17" ht="15.75" spans="1:3">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="4" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="18" ht="15.75" spans="1:3">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="4" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="19" ht="15.75" spans="1:3">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="20" ht="15.75" spans="1:3">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="21" ht="15.75" spans="1:3">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="22" ht="15.75" spans="1:3">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="23" ht="15.75" spans="1:3">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="4" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="24" ht="15.75" spans="1:3">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="4" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="25" ht="15.75" spans="1:3">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="4" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="26" ht="15.75" spans="1:3">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="27" ht="15.75" spans="1:3">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="4" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="28" ht="15.75" spans="1:3">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="4" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="29" ht="15.75" spans="1:3">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="30" ht="15.75" spans="1:3">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="4" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="31" ht="15.75" spans="1:3">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="4" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="32" ht="15.75" spans="1:3">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="4" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="33" ht="15.75" spans="1:3">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="34" ht="15.75" spans="1:3">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="35" ht="15.75" spans="1:3">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="36" ht="15.75" spans="1:3">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="5" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="37" ht="15.75" spans="1:3">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="4" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="38" ht="15.75" spans="1:3">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="4" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="39" ht="15.75" spans="1:3">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="40" ht="15.75" spans="1:3">
-      <c r="A40" s="9" t="s">
+      <c r="A40" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="4" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="41" ht="15.75" spans="1:3">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="42" ht="15.75" spans="1:3">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="43" ht="15.75" spans="1:3">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="5" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="44" ht="15.75" spans="1:3">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="5" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="45" ht="15.75" spans="1:3">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="4" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="46" ht="15.75" spans="1:3">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="4" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="47" ht="15.75" spans="1:3">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="48" ht="15.75" spans="1:3">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="49" ht="15.75" spans="1:3">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="50" ht="15.75" spans="1:3">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C50" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="51" ht="15.75" spans="1:3">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="4" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="52" ht="15.75" spans="1:3">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="53" ht="15.75" spans="1:3">
-      <c r="A53" s="3" t="s">
+      <c r="A53" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C53" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="54" ht="15.75" spans="1:3">
-      <c r="A54" s="3" t="s">
+      <c r="A54" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C54" s="4" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="55" ht="15.75" spans="1:3">
-      <c r="A55" s="3" t="s">
+      <c r="A55" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C55" s="4" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="56" ht="15.75" spans="1:3">
-      <c r="A56" s="3" t="s">
+      <c r="A56" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C56" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="57" ht="15.75" spans="1:3">
-      <c r="A57" s="3" t="s">
+      <c r="A57" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B57" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="C57" s="5" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="58" ht="15.75" spans="1:3">
-      <c r="A58" s="3" t="s">
+      <c r="A58" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B58" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C58" s="4" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="59" ht="15.75" spans="1:3">
-      <c r="A59" s="3" t="s">
+      <c r="A59" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C59" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="60" ht="15.75" spans="1:3">
-      <c r="A60" s="3" t="s">
+      <c r="A60" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C60" s="4" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="61" ht="15.75" spans="1:3">
-      <c r="A61" s="10" t="s">
+      <c r="A61" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="B61" s="10" t="s">
+      <c r="B61" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="C61" s="10" t="s">
+      <c r="C61" s="11" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="62" ht="15.75" spans="1:3">
-      <c r="A62" s="3" t="s">
+      <c r="A62" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B62" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C62" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="63" ht="15.75" spans="1:3">
-      <c r="A63" s="3" t="s">
+      <c r="A63" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B63" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C63" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="64" ht="15.75" spans="1:3">
-      <c r="A64" s="3" t="s">
+      <c r="A64" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B64" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C64" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="65" ht="15.75" spans="1:3">
-      <c r="A65" s="3" t="s">
+      <c r="A65" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B65" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C65" s="4" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="66" ht="15.75" spans="1:3">
-      <c r="A66" s="3" t="s">
+      <c r="A66" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B66" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="C66" s="5" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="67" ht="15.75" spans="1:3">
-      <c r="A67" s="3" t="s">
+      <c r="A67" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B67" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C67" s="4" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="68" ht="15.75" spans="1:3">
-      <c r="A68" s="3" t="s">
+      <c r="A68" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B68" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C68" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="69" ht="15.75" spans="1:3">
-      <c r="A69" s="3" t="s">
+      <c r="A69" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B69" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C69" s="4" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="70" ht="15.75" spans="1:3">
-      <c r="A70" s="3" t="s">
+      <c r="A70" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B70" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C70" s="4" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="71" ht="15.75" spans="1:3">
-      <c r="A71" s="3" t="s">
+      <c r="A71" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B71" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C71" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="72" ht="15.75" spans="1:3">
-      <c r="A72" s="10" t="s">
+      <c r="A72" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="B72" s="10" t="s">
+      <c r="B72" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="C72" s="4" t="s">
+      <c r="C72" s="5" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="73" ht="15.75" spans="1:3">
-      <c r="A73" s="3" t="s">
+      <c r="A73" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B73" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C73" s="4" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="74" ht="15.75" spans="1:3">
-      <c r="A74" s="3" t="s">
+      <c r="A74" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B74" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C74" s="5" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="75" ht="15.75" spans="1:3">
-      <c r="A75" s="3" t="s">
+      <c r="A75" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B75" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="C75" s="4" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="76" ht="15.75" spans="1:3">
-      <c r="A76" s="3" t="s">
+      <c r="A76" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B76" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C76" s="4" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="77" ht="15.75" spans="1:3">
-      <c r="A77" s="3" t="s">
+      <c r="A77" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B77" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="C77" s="4" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="78" ht="15.75" spans="1:3">
-      <c r="A78" s="3" t="s">
+      <c r="A78" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="B78" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="C78" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="79" ht="15.75" spans="1:3">
-      <c r="A79" s="3" t="s">
+      <c r="A79" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B79" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C79" s="4" t="s">
+      <c r="C79" s="5" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="80" ht="15.75" spans="1:3">
-      <c r="A80" s="3" t="s">
+      <c r="A80" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="B80" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="C80" s="4" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="81" ht="15.75" spans="1:3">
-      <c r="A81" s="3" t="s">
+      <c r="A81" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="B81" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="C81" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="82" ht="15.75" spans="1:3">
-      <c r="A82" s="3" t="s">
+      <c r="A82" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="B82" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="C82" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="83" ht="15.75" spans="1:3">
-      <c r="A83" s="3" t="s">
+      <c r="A83" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="B83" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="C83" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="84" ht="15.75" spans="1:3">
-      <c r="A84" s="11" t="s">
+      <c r="A84" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="B84" s="11" t="s">
+      <c r="B84" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="C84" s="11" t="s">
+      <c r="C84" s="12" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="85" ht="15.75" spans="1:3">
-      <c r="A85" s="11" t="s">
+      <c r="A85" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="B85" s="11" t="s">
+      <c r="B85" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="C85" s="11" t="s">
+      <c r="C85" s="12" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="86" ht="15.75" spans="1:3">
-      <c r="A86" s="11" t="s">
+      <c r="A86" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="B86" s="11" t="s">
+      <c r="B86" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="C86" s="11" t="s">
+      <c r="C86" s="12" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="87" ht="15.75" spans="1:3">
-      <c r="A87" s="12" t="s">
+      <c r="A87" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="B87" s="12" t="s">
+      <c r="B87" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="C87" s="12" t="s">
+      <c r="C87" s="13" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="88" ht="15.75" spans="1:3">
-      <c r="A88" s="9" t="s">
+      <c r="A88" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="B88" s="9" t="s">
+      <c r="B88" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="C88" s="12" t="s">
+      <c r="C88" s="13" t="s">
         <v>41</v>
       </c>
     </row>
@@ -3283,77 +3289,77 @@
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:1">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:1">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:1">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:1">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:1">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:1">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:1">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:1">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="7" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="6" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="6" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="6" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="6" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3427,7 +3433,7 @@
       <c r="C4" t="s">
         <v>233</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>234</v>
       </c>
     </row>
@@ -3456,119 +3462,119 @@
         <v>239</v>
       </c>
       <c r="D6" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B7">
         <v>1234</v>
       </c>
       <c r="C7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D7" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B8">
         <v>1234</v>
       </c>
       <c r="C8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D8" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B9">
         <v>1234</v>
       </c>
       <c r="C9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D9" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B10">
         <v>1234</v>
       </c>
       <c r="C10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D10" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B11">
         <v>1234</v>
       </c>
       <c r="C11" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D11" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B12">
         <v>1234</v>
       </c>
       <c r="C12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D12" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="2" t="s">
-        <v>252</v>
+      <c r="A13" s="3" t="s">
+        <v>253</v>
       </c>
       <c r="B13">
         <v>1234</v>
       </c>
       <c r="C13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D13" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B14">
         <v>1234</v>
       </c>
       <c r="C14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D14" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
